--- a/contact_forms/023_prospect_information_collection_form--contact_forms.xlsx
+++ b/contact_forms/023_prospect_information_collection_form--contact_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'entry_level',_'value':_'entry_level'}</t>
+          <t>entry_level</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Entry Level', 'value': 'entry_level'}</t>
+          <t>Entry Level</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'management',_'value':_'management'}</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Management', 'value': 'management'}</t>
+          <t>Management</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'leadership',_'value':_'leadership'}</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Leadership', 'value': 'leadership'}</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'executive',_'value':_'executive'}</t>
+          <t>executive</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Executive', 'value': 'executive'}</t>
+          <t>Executive</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'monday',_'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Monday', 'value': 'monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'tuesday',_'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Tuesday', 'value': 'tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'wednesday',_'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Wednesday', 'value': 'wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'thursday',_'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Thursday', 'value': 'thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'friday',_'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Friday', 'value': 'friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'saturday',_'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Saturday', 'value': 'saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'sunday',_'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Sunday', 'value': 'sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'morning',_'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Morning', 'value': 'morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'evening',_'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Evening', 'value': 'evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'anytime',_'value':_'anytime'}</t>
+          <t>anytime</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Anytime', 'value': 'anytime'}</t>
+          <t>Anytime</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'open',_'value':_'open'}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Open', 'value': 'open'}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'not_specified',_'value':_'not_specified'}</t>
+          <t>not_specified</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Not Specified', 'value': 'not_specified'}</t>
+          <t>Not Specified</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'temporary',_'value':_'temporary'}</t>
+          <t>temporary</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Temporary', 'value': 'temporary'}</t>
+          <t>Temporary</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'high'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'not_specified',_'value':_'not_specified'}</t>
+          <t>not_specified</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Not Specified', 'value': 'not_specified'}</t>
+          <t>Not Specified</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'ongoing',_'value':_'ongoing'}</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Ongoing', 'value': 'ongoing'}</t>
+          <t>Ongoing</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'as_needed',_'value':_'as_needed'}</t>
+          <t>as_needed</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'As needed', 'value': 'as_needed'}</t>
+          <t>As needed</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'referral',_'value':_'referral'}</t>
+          <t>referral</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Referral', 'value': 'referral'}</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'in_person',_'value':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'In Person', 'value': 'in_person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
